--- a/www/flightdata/xlsx/eoss-350.xlsx
+++ b/www/flightdata/xlsx/eoss-350.xlsx
@@ -3150,7 +3150,7 @@
         <v>24134.98</v>
       </c>
       <c r="I2">
-        <v>524</v>
+        <v>388</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
